--- a/AAII_Financials/Quarterly/BBVA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBVA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>BBVA</t>
   </si>
@@ -656,272 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10365600</v>
+      </c>
+      <c r="E8" s="3">
         <v>10472700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9656000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9098900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8865500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8776500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8486400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8362700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8781700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8270600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7152600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8114900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7162700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7021900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10275200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9459400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8087800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6476400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4311500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4041600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7358400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5801000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3238600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6138100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5894200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7009100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4937600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9444700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9306500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>9290900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9602800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7979200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8096600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7902300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8790800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8029000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>8211800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>8200200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>8301200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>8139200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1042,53 +1048,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>10365600</v>
+      </c>
+      <c r="E10" s="3">
         <v>10472700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9656000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9098900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8865500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8776500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8486400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8362700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8781700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8270600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7152600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8114900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7162700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7021900</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1164,8 +1173,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1330,8 +1343,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,53 +1468,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>295900</v>
+      </c>
+      <c r="E14" s="3">
         <v>302100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>297100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>289800</v>
       </c>
-      <c r="G14" s="3">
-        <v>243100</v>
-      </c>
       <c r="H14" s="3">
+        <v>241900</v>
+      </c>
+      <c r="I14" s="3">
         <v>239900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>394500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>304500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>503600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>878200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1012900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>433400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>547600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1574,130 +1593,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>370200</v>
+      </c>
+      <c r="E15" s="3">
         <v>375900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>182000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>344900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>339400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>317800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>167500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>319000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>317200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>312900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>157000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>309100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>286000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>284700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-373300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-365300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-368900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-339600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-330700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-338100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-974400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-326900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-156600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-379900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-746200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-809500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-216800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-493700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-467000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-470100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-358400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-330100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-334500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-333800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-371400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-387100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-401700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-415500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-427300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-436700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4518500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4727300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4741100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4269600</v>
       </c>
-      <c r="G17" s="3">
-        <v>3835600</v>
-      </c>
       <c r="H17" s="3">
+        <v>3836800</v>
+      </c>
+      <c r="I17" s="3">
         <v>3837000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4201300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3745300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3647300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3661700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3511700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3540400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3259800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3275700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5477100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4767000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3859500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2939300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>902000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>669800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1671600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3130600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1553900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2854200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3541100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4934200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2933400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5366700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4820900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5221400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5635300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4395000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4139100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4117500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4514900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4194000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4308400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4239800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3900600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4235100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5847100</v>
+      </c>
+      <c r="E18" s="3">
         <v>5745400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4914900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4829300</v>
       </c>
-      <c r="G18" s="3">
-        <v>5029900</v>
-      </c>
       <c r="H18" s="3">
+        <v>5028800</v>
+      </c>
+      <c r="I18" s="3">
         <v>4939500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4285100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4617400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5134500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4608900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3641000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4574500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3902800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3746200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4798100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4692400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4228400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3537100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3409500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3371800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5686800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2670400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1684600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3283900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2353100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2074900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2004200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4078000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4485600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4069500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3967400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3584200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3957500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3784800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4275900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3903400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3960400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>4400600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3904100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,17 +2057,18 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
@@ -2069,208 +2102,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1964900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1465400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1509200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1123000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1177300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-896000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2630200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-809400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1944900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1232000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1316700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1194500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-753100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1767700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2022200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1727300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2115000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-887200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1437700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1404300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3248200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1611200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1695300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1536500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2892300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-1889800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6217300</v>
+      </c>
+      <c r="E21" s="3">
         <v>6122400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5096900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5174200</v>
       </c>
-      <c r="G21" s="3">
-        <v>5369300</v>
-      </c>
       <c r="H21" s="3">
+        <v>5368200</v>
+      </c>
+      <c r="I21" s="3">
         <v>5257200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4452600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4936400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5451600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4921800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3797900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4883600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4188900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4030900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3207600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3592200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3095600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2746100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>825200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>2431800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>1469000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2804000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2931600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2811100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2213200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3026000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2851000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2717600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1398000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2610900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2609700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2839400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1936800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2450900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2313,8 +2352,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2391,252 +2430,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5551200</v>
+      </c>
+      <c r="E23" s="3">
         <v>5444500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4617800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4539500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4786800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4699500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3890700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4313000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4630900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3730700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3240900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3561600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3469400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3198600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2833200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3227000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2719200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2414100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2232200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2475800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3056600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1861000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3629500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2051900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1036400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>880400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1251000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2310300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2463400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2342200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1852400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2697000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2519800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2380500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1027700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2223800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2208100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2423900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1508300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2014300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1802800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1768700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1488800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1415000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1362300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1584500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1212300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1264800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1472200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1241800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>883200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1297600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1122300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1032200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>941500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1086100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>812800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>979800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>528000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>689200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>827400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>517400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>478800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>543900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>297800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>222500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>361300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>596600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>678800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>668700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>408100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>732100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>660100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>677500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>559900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>617100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>613700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>672600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>368600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>545800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3748400</v>
+      </c>
+      <c r="E26" s="3">
         <v>3675800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3129000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3124500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3424500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3115000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2678300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3048200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3158700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2488900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2357700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2264000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2347200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2166400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1891800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2140900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1906400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1434400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1704200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1786600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2229200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1343700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3150800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1508100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>738500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>657800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>889700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1713800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1784600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1673500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1444300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1964900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1859700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1703000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>467900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1606700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1594300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1751300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1139800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1468400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3498200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3446300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2507900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2969600</v>
       </c>
-      <c r="G27" s="3">
-        <v>3345900</v>
-      </c>
       <c r="H27" s="3">
+        <v>3228400</v>
+      </c>
+      <c r="I27" s="3">
         <v>2916100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2116200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2931100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3086900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2279600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1893400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2204700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2218300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2005600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1648100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1905300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1686600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1349700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1064600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1507700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1512900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1092900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3041100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1185300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>559600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>471300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>680800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1500600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1502300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1393600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>901400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1854100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1507400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1414200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-259200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1282400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1242000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1407400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>490700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1132700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3186,34 +3246,34 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>296200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>187300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1724500</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>130900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-2426200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-855900</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,17 +3555,20 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
@@ -3533,208 +3602,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1964900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1465400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1509200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1123000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1177300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>896000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2630200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>809400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1944900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1232000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1316700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1194500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>753100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1767700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2022200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1727300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2115000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>887200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1437700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1404300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3248200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1611200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1695300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1536500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2892300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>1889800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3498200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3446300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2974100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2969600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3228400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2916100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2517900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2931100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2993700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2373500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2274800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2204700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2218300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2005600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1648100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1905300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1686600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1349700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1064600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1507700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1809200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1280200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1316600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1185300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>690500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1954900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-175000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1500600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1502300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1393600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>901400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1854100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1507400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1414200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-259200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1282400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1242000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1407400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>490700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1132700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3498200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3446300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2974100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2969600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3228400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2916100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2517900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2931100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2993700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2373500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2274800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2204700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2218300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2005600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1648100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1905300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1686600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1349700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1064600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1507700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1809200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1280200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1316600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1185300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>690500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1954900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-175000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1500600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1502300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1393600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>901400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1854100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1507400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1414200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-259200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1282400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1242000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1407400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>490700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1132700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,296 +4277,303 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19439000</v>
+      </c>
+      <c r="E41" s="3">
         <v>18488400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18763600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17128900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15690000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16472100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16397100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17205000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16982700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17466800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16212000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13958500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14159400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>90468300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>110968200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>119820500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>110191900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>94847400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>73500900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68094500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>83194800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>76084000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>86079600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>94407400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>93264100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>74616100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>70260500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>74219700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>71743900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>78765000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>84342000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>66627700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>60221300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>66888000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>85541600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>108471700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>81679800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>110202000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>94252200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>83864000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>190286800</v>
+      </c>
+      <c r="E42" s="3">
         <v>166963000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>155607600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>130943300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>137054600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>111021400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>123677400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>143627000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>133935500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>157267200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>163926200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>144226300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>156740200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>130244500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>206733500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>208218500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>210745400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>202353600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>141660400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>125016200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>197938000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>192677700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>183147600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>195442800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>216004500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>145503400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>193548100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>226342600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>209586200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>194436300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>184288700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>178546200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>180681700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>178388800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>156365000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>171839500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>174756700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>195521500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>196691800</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>204585700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3434300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2535500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4694100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4035000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4007000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3365800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4446600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4001800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3560500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2738200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3161300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2546600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2449800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4558,52 +4650,55 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2364900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2312900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2149800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2368900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2389900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2239500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1976400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1129800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1147500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1188900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1016900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1785600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1581900</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4680,52 +4775,55 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7823600</v>
+      </c>
+      <c r="E45" s="3">
         <v>7762000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2684000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2645800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2503800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2337900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2153400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2240700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2056100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1779000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1820500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1797200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1484700</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>277045600</v>
+      </c>
+      <c r="E46" s="3">
         <v>232506600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>234217400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207017500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>192951300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>173445700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>185204500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>216344000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>188974600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>245532400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>253285100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>221120900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>240704100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>220712700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,374 +5025,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>170872800</v>
+      </c>
+      <c r="E47" s="3">
         <v>171671900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>169626600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162476800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>157931900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>145656100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>134594700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>143389500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>140614000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>136226100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>134873400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>128991300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>129258700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>128321400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2029100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>975900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>973800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>988400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>975700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>947700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1481200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1498100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1433300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1288000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1490200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1570900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1680100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1898700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1926900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1898400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1866600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1076600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1628200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1531700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1781700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1777200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1281300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1352200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>898000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>881500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10875100</v>
+      </c>
+      <c r="E48" s="3">
         <v>10852100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10941600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10577300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10530800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10009700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9922400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10109300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10077100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10164000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10090600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9657100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9402800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9718600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9677100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9258400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9071500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8001900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7452100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7851700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7745600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8150800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7802700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9019400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9879300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10193500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11367800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12504700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12119300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12451200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>8551200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7406500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7460800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7628900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>8068200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8932200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>9212700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>10493900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10496200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>11116000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3567900</v>
+      </c>
+      <c r="E49" s="3">
         <v>3384100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3352100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3129200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3010000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2693500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2577900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2589800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2550100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2596800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2611900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2445000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2493400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2388000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2389400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2327400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2413000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2381800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2445600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2436600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2430200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2338900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4534600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5043300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5129500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7866400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10422200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9719400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10027700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9834600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9096700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9273900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9002500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9496500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9809600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>10150600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11222800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>11486900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>11154700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2756800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3210000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2276600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3054100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2191400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2402700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2825300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2683500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2516900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2976600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1712200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1906200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3306800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24539300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17465700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16917300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17266000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17687700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1150200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>17229500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>110039400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>101050600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>19294600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20444700</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>20772100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>22797100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>20027000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20673900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>20484300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>23245200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>43002600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>42532100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>43284100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>20375300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>21308800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>22578200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>23469200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>22457300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1102965800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1031093000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1009247400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>953963400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>912476800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>835347000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>799670800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>858064900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>813815500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>864915300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>857254300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>802006800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>832375500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>803524600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>788713100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>798291500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>778311400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>733288600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>718633600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>701960000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>685762800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>761447900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>731889100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>754567800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>822354100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>797371200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>787814800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>868538700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>820687200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>826813400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>800455400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>740967800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>763836400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>752614200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>774239300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>775067300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>788118300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>844195900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>859059900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>850574400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,172 +6117,176 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>629663000</v>
+      </c>
+      <c r="E57" s="3">
         <v>608423800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>617847800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>581267200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>549061700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>512706400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>484961200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>499466900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>482194400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>487582300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>488407200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>457337000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>470093900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>511722100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6283400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7474100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6733200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8122300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6642300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>4765200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5310100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4987000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4822100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4950500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5074200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6154300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6685500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7354200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6681000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5917900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5520300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6448600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>6241600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6019500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>5918500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>8067600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7665000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>7767100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>96558900</v>
+      </c>
+      <c r="E58" s="3">
         <v>84361800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>74766900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69389900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>78690500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>63890000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>67079400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>78435200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>69895000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>82337900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>75561000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>78840000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>80661600</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6200,11 +6333,11 @@
         <v>0</v>
       </c>
       <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>10034900</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6214,8 +6347,8 @@
       <c r="AJ58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
@@ -6232,175 +6365,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>108742100</v>
+      </c>
+      <c r="E59" s="3">
         <v>94155400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>80443800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>71520600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>69147400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58468400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61769300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83376100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72856500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>92402600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>104652400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>88662200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104074200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>116454800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4442600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4307700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3313300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1510300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>698200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>716300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>381900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>544600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>322800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>612000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>993600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>622300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1263500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1870900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1455000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>995700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1581700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1424100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1249900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1727900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1125400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1869900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2114000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1130400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>839152300</v>
+      </c>
+      <c r="E60" s="3">
         <v>790702200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>777124600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>726287700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700234900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>637856700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>616985200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>664800400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>627988900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>665208800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>671801700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>627999600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>657585200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>628176900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,252 +6615,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>130724300</v>
+      </c>
+      <c r="E61" s="3">
         <v>110169500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>104584900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>98674200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>89377600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>84314700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>78611700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>81619500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>80328900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>85569100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>82006200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>74539600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>74461800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>59306800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>66583400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>64019600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>64177200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>64260200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>66909600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>59657000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>64937900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>67733200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>68805600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>77133600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>78275000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>70840400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>81243300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>81717900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>82456200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>74601000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>75670100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>68695600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>69057800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>66830900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>71712000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>77737100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>77992900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>85500300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>89649700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>89924400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53930100</v>
+      </c>
+      <c r="E62" s="3">
         <v>54561300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48948000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50381300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45166200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>43795900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36569000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42139200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38785000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48342900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37183600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37472500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37348300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>60118400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7147300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6908900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6905100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7714400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8302000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>8764500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>90422000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>83179200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>10286600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11161100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>11314700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12531600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10533500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10280100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10430800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9972800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>28931600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>29070600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>30134400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>11784300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>12393500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>14271200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>14629200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>14387400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1030086800</v>
+      </c>
+      <c r="E66" s="3">
         <v>960987000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>936691300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>881442000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>840971200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>771291600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>737539100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>794745700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>752645500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>804736200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>796167800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>745430800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>774986900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>747602100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>736773300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>748316700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>728866000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>686633600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>671034000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>653565200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>638664900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>713504600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>687456000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>709815700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>774660600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>743726800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>732800600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>806395000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>763218900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>769600400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>744729000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>690021500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>713162600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>702950600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>722241800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>721962400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>734451300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>787801400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>803463600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>794739800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7618,8 +7785,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65682600</v>
+      </c>
+      <c r="E72" s="3">
         <v>62823700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>64596700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>61674300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>61039300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53264200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50811700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52142500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>49168500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46577800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>47866700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43706600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43948700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>45315200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42228400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40983300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37094000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>37241000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>65283800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34905500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34679100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31730300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31604100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31933100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>53644400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37013000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36668900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33852100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32793800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33457100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>33603500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>31814700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>30053400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>30401400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>32527600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>31246300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>31554400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>31805600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>31054300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>67350600</v>
+      </c>
+      <c r="E76" s="3">
         <v>64878400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>67341800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>67634600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66738700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59529800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>57618800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58988400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57043800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>56106400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57147100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52656600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53549100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>51924200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51939800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49974800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49445400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46655000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>47599600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>48394800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47097900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47943300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>44433200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>44752200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47693500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53644400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>55014300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>62143700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>57468300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>57213000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>55726400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>50946300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>50673800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>49663600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>51997500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>53104900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>53667000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>56394500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>55596300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>55834600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3498200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3446300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2974100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2969600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3228400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2916100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2517900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2931100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2993700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2373500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2274800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2204700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2218300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2005600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1648100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1905300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1686600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1349700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1064600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1507700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1809200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1280200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1316600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1185300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>690500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1954900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-175000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1500600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1502300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1393600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>901400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1854100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1507400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1414200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-259200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1282400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1242000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1407400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>490700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1132700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>268900</v>
+      </c>
+      <c r="E83" s="3">
         <v>256200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-139800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>257600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>263600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>255700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-186800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>251900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>223800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>228200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-162400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>202000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>374400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>365300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>376500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>332000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>-1035800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>379900</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>458400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>493700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>468200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>468900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>360800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>329000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>331200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>337100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>370300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>387100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>401700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>415500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>428400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>436700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25986500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11253300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4703500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20145500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7475000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>169700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6936500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17408000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28827800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-208200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12256000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4557600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12243400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4033000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5492600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8859600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18408500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3864800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-51121500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>7286100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>5807000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>673700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4700900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-11856700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10952500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6121700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-7505100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1360400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5143200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-924500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5509000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-7763600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>9182700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>4989900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-223900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-258300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-474300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-204200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-138600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-141600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-362400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-319000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-297900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-303200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-151400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-558800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-216200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-289000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-339000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-373000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1619000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-111000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-666000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-157000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>663400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-41500</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>272100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-515700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-681100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-85300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-183400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-166100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-517200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-126800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-112700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1055300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-819300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-405600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-494600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-561200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-444700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-319400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-296200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-266100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-488500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-379300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-403500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-190100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-653000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-301300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-384600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-25500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-379300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3851900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>138600</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-141200</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>1213800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-464300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-515300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-191400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>4383800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>4315200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-139600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>43900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2040900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-405000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1308200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>326300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1783000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-441400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,62 +10427,63 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>3835300</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>2159200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>2768100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>1726900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>2405400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>1051200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>2027300</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-799700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1591900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -10261,11 +10494,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>1126800</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10276,49 +10509,52 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-877300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-120000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1368200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-130400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1171100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>136200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1239400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-132900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-796600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-122300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-280500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-738300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-197200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,370 +10925,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5007400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3365600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2104000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>326200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3112200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>530700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1170900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>654700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3388000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1228800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1620400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-92100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>173600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-486700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-933700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2397000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3434000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1460400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>975500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1095000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1275900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>839100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3072800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>424700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1010200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2810000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1845300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-38400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>664200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>541900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-302900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-757100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-611600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1294200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1204100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>667800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2479400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1122900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>577200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-986000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-84100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>653000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2666500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>920800</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-2763500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1014800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>380800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>996000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>5396900</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-1706300</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-2892800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1275200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1050500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2933100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2852000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3236400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1227200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-965100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2674800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1146700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1003100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>39900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1322900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1428500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20760900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14688100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2008900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20073900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12200800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-799800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7705800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15094800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-33718000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1194300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9459500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5291100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12455200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3814600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9215200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7098000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11503400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3403600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-44610600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>6533600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>4919500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2208700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7489000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8690400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>17178100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4390500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10530000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>215200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>5173500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1008700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>4585600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-8457300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>8885700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>2508400</v>
       </c>
     </row>
